--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-06-2025.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>£19.28</t>
+          <t>£20.73</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>£22.25</t>
+          <t>£23.92</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>£26.04</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>£28.08</t>
+          <t>£30.19</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>£33.40</t>
+          <t>£35.91</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>£40.56</t>
+          <t>£43.61</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>£41.94</t>
+          <t>£45.09</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>£44.72</t>
+          <t>£48.08</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>£49.42</t>
+          <t>£53.13</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>£50.61</t>
+          <t>£54.41</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>£62.22</t>
+          <t>£66.89</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>£68.65</t>
+          <t>£73.80</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4130-2400x1200x130mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>£73.34</t>
+          <t>£78.85</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>£76.33</t>
+          <t>£82.06</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>£63.54</t>
+          <t>£68.31</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>£73.60</t>
+          <t>£79.12</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>£81.27</t>
+          <t>£87.37</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>£86.34</t>
+          <t>£92.82</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>£63.65</t>
+          <t>£68.43</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>£66.62</t>
+          <t>£71.62</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>£67.17</t>
+          <t>£72.21</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>£1812.16</t>
+          <t>£1948.16</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>£2007.36</t>
+          <t>£2157.92</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
